--- a/resources/templates/standard/B2300-03.xlsx
+++ b/resources/templates/standard/B2300-03.xlsx
@@ -29,7 +29,7 @@
     <t>대표이사</t>
   </si>
   <si>
-    <t>※ HKMC 『협력사 현장 작업자 정성작업 유도방안』 점검 체크시트 인용</t>
+    <t>※ 고객사 『협력사 현장 작업자 정성작업 유도방안』 점검 체크시트 인용</t>
   </si>
   <si>
     <t>1.현 황</t>
